--- a/reports/一级子公司B_现金流量表_2026-04.xlsx
+++ b/reports/一级子公司B_现金流量表_2026-04.xlsx
@@ -1957,16 +1957,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F3" s="28" t="inlineStr">
-        <is>
-          <t>－</t>
-        </is>
-      </c>
-      <c r="G3" s="28" t="inlineStr">
-        <is>
-          <t>－</t>
-        </is>
-      </c>
+      <c r="F3" s="28" t="n"/>
+      <c r="G3" s="28" t="n"/>
       <c r="I3" s="5" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1">
@@ -1996,10 +1988,10 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>48204000</v>
+        <v>46570534</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>181247040</v>
+        <v>175804280</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2030,10 +2022,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>1018395</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0</v>
+        <v>3818765</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2063,10 +2055,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0</v>
+        <v>505321</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0</v>
+        <v>1902289</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2096,10 +2088,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0</v>
+        <v>253993</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0</v>
+        <v>955449</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2129,10 +2121,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0</v>
+        <v>202725</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0</v>
+        <v>760669</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2162,10 +2154,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0</v>
+        <v>151912</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0</v>
+        <v>573165</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2195,10 +2187,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0</v>
+        <v>101676</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0</v>
+        <v>380590</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2228,10 +2220,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0</v>
+        <v>75752</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0</v>
+        <v>286272</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2261,10 +2253,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0</v>
+        <v>50938</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0</v>
+        <v>190560</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2294,10 +2286,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0</v>
+        <v>126116</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0</v>
+        <v>476382</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2327,10 +2319,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0</v>
+        <v>64004</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0</v>
+        <v>239791</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2360,10 +2352,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0</v>
+        <v>40137</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0</v>
+        <v>151256</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2393,10 +2385,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>154500</v>
+        <v>150434</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>580920</v>
+        <v>565260</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2426,10 +2418,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>927000</v>
+        <v>898700</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>3485520</v>
+        <v>3375737</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2546,7 +2538,7 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>49285500</v>
+        <v>50210637</v>
       </c>
       <c r="G21" s="20" t="n"/>
     </row>
@@ -2577,10 +2569,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n">
-        <v>24720000</v>
+        <v>23883440</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>92947200</v>
+        <v>90250730</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2610,10 +2602,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>339684</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>1271731</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2643,10 +2635,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>252337</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
+        <v>951836</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2676,10 +2668,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>169627</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>636686</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -2709,10 +2701,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>126440</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
+        <v>475470</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2742,10 +2734,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>0</v>
+        <v>84579</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0</v>
+        <v>318500</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2775,10 +2767,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n">
-        <v>0</v>
+        <v>63744</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>0</v>
+        <v>238956</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2808,10 +2800,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n">
-        <v>8755000</v>
+        <v>8481032</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>32918800</v>
+        <v>32022259</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2841,10 +2833,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n">
-        <v>3296000</v>
+        <v>3211337</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>12392960</v>
+        <v>12015523</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2874,10 +2866,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n">
-        <v>1854000</v>
+        <v>1791930</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>6971040</v>
+        <v>6772384</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2936,7 +2928,7 @@
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>38625000</v>
+        <v>38404150</v>
       </c>
       <c r="G33" s="20" t="n"/>
     </row>
@@ -2967,7 +2959,7 @@
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>10660500</v>
+        <v>11806487</v>
       </c>
       <c r="G34" s="20" t="n"/>
     </row>
@@ -3093,10 +3085,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n">
-        <v>61800</v>
+        <v>59928</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>247200</v>
+        <v>240554</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3159,10 +3151,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n">
-        <v>618000</v>
+        <v>597662</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>2472000</v>
+        <v>2403220</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3192,10 +3184,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n">
-        <v>370800</v>
+        <v>361689</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>1483200</v>
+        <v>1439107</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3225,7 +3217,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>679800</v>
+        <v>657590</v>
       </c>
       <c r="G42" s="20" t="n"/>
     </row>
@@ -3256,10 +3248,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n">
-        <v>6180000</v>
+        <v>6028685</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>24720000</v>
+        <v>24022468</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3289,10 +3281,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n">
-        <v>927000</v>
+        <v>896343</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>3708000</v>
+        <v>3594213</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3322,10 +3314,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n">
-        <v>4326000</v>
+        <v>4212272</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>17304000</v>
+        <v>16835460</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3454,10 +3446,10 @@
         </is>
       </c>
       <c r="F49" s="15" t="n">
-        <v>144200</v>
+        <v>139563</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>576800</v>
+        <v>560982</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3487,7 +3479,7 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>6324200</v>
+        <v>6168248</v>
       </c>
       <c r="G50" s="20" t="n"/>
     </row>
@@ -3518,7 +3510,7 @@
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>-5644400</v>
+        <v>-5510658</v>
       </c>
       <c r="G51" s="20" t="n"/>
     </row>
@@ -3578,10 +3570,10 @@
         </is>
       </c>
       <c r="F53" s="15" t="n">
-        <v>1236000</v>
+        <v>1194481</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>4944000</v>
+        <v>4794383</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3644,10 +3636,10 @@
         </is>
       </c>
       <c r="F55" s="15" t="n">
-        <v>2060000</v>
+        <v>1995049</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>8240000</v>
+        <v>7982164</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3677,10 +3669,10 @@
         </is>
       </c>
       <c r="F56" s="15" t="n">
-        <v>2060000</v>
+        <v>2001919</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>8240000</v>
+        <v>8019457</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3710,10 +3702,10 @@
         </is>
       </c>
       <c r="F57" s="15" t="n">
-        <v>61800</v>
+        <v>60039</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>247200</v>
+        <v>239428</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -3743,7 +3735,7 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>3357800</v>
+        <v>3249569</v>
       </c>
       <c r="G58" s="20" t="n"/>
     </row>
@@ -3774,10 +3766,10 @@
         </is>
       </c>
       <c r="F59" s="15" t="n">
-        <v>1648000</v>
+        <v>1605633</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>6592000</v>
+        <v>6390001</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3807,10 +3799,10 @@
         </is>
       </c>
       <c r="F60" s="15" t="n">
-        <v>1648000</v>
+        <v>1592849</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>6592000</v>
+        <v>6405638</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3840,10 +3832,10 @@
         </is>
       </c>
       <c r="F61" s="15" t="n">
-        <v>288400</v>
+        <v>281386</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>1153600</v>
+        <v>1119879</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3902,10 +3894,10 @@
         </is>
       </c>
       <c r="F63" s="15" t="n">
-        <v>247200</v>
+        <v>241048</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>988800</v>
+        <v>961335</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3935,10 +3927,10 @@
         </is>
       </c>
       <c r="F64" s="15" t="n">
-        <v>36050</v>
+        <v>34882</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>144200</v>
+        <v>139726</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -3968,7 +3960,7 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>1972450</v>
+        <v>1921901</v>
       </c>
       <c r="G65" s="20" t="n"/>
     </row>
@@ -3999,7 +3991,7 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>1385350</v>
+        <v>1327668</v>
       </c>
       <c r="G66" s="20" t="n"/>
     </row>
@@ -4059,7 +4051,7 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>6401450</v>
+        <v>7623497</v>
       </c>
       <c r="G68" s="20" t="n"/>
     </row>
@@ -4090,7 +4082,9 @@
         </is>
       </c>
       <c r="F69" s="23" t="n"/>
-      <c r="G69" s="20" t="n"/>
+      <c r="G69" s="20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="9" t="inlineStr">
@@ -4119,7 +4113,7 @@
         </is>
       </c>
       <c r="F70" s="26" t="n">
-        <v>6401450</v>
+        <v>7623497</v>
       </c>
       <c r="G70" s="26" t="n"/>
     </row>
